--- a/output/tables/signal_summary.xlsx
+++ b/output/tables/signal_summary.xlsx
@@ -40,10 +40,10 @@
     <t>0.8</t>
   </si>
   <si>
-    <t>3.2 天</t>
-  </si>
-  <si>
-    <t>96.4%</t>
+    <t>3.0 天</t>
+  </si>
+  <si>
+    <t>91.1%</t>
   </si>
   <si>
     <t>2.0 天</t>
